--- a/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
@@ -10,13 +10,14 @@
     <sheet name="Weekly Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Category Aggregation" sheetId="2" r:id="rId2"/>
     <sheet name="Quantity Pivot" sheetId="3" r:id="rId3"/>
+    <sheet name="Sample Statistics" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>文件名称</t>
   </si>
@@ -100,6 +101,12 @@
   </si>
   <si>
     <t>汇总</t>
+  </si>
+  <si>
+    <t>提示</t>
+  </si>
+  <si>
+    <t>今日无样品数据</t>
   </si>
 </sst>
 </file>
@@ -695,4 +702,27 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,10 +43,16 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>全部 笔订单-2026-02-28-16_48.csv</t>
-  </si>
-  <si>
-    <t>22/02/2026</t>
+    <t>03-02.csv</t>
+  </si>
+  <si>
+    <t>03-03.csv</t>
+  </si>
+  <si>
+    <t>02/03/2026</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -58,6 +64,9 @@
     <t>销售额</t>
   </si>
   <si>
+    <t>汇率后(销售额)</t>
+  </si>
+  <si>
     <t>P列折后价</t>
   </si>
   <si>
@@ -70,9 +79,6 @@
     <t>寄样支出</t>
   </si>
   <si>
-    <t>汇率后(销售额)</t>
-  </si>
-  <si>
     <t>精华液</t>
   </si>
   <si>
@@ -91,22 +97,16 @@
     <t>身体乳单瓶</t>
   </si>
   <si>
-    <t>身体乳双瓶</t>
-  </si>
-  <si>
-    <t>身体乳三瓶</t>
-  </si>
-  <si>
     <t>精华液单瓶</t>
   </si>
   <si>
+    <t>精华液双瓶</t>
+  </si>
+  <si>
     <t>汇总</t>
   </si>
   <si>
-    <t>提示</t>
-  </si>
-  <si>
-    <t>今日无样品数据</t>
+    <t>总样品数</t>
   </si>
 </sst>
 </file>
@@ -464,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -498,25 +498,51 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>1883222</v>
+      </c>
+      <c r="D2">
+        <v>523.12</v>
+      </c>
+      <c r="E2">
+        <v>1681343</v>
+      </c>
+      <c r="F2">
+        <v>95.66</v>
+      </c>
+      <c r="G2">
+        <v>55.2</v>
+      </c>
+      <c r="H2">
+        <v>40.42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="C2">
-        <v>2715953</v>
-      </c>
-      <c r="D2">
-        <v>754.4299999999999</v>
-      </c>
-      <c r="E2">
-        <v>2700953</v>
-      </c>
-      <c r="F2">
-        <v>261.28</v>
-      </c>
-      <c r="G2">
-        <v>153.72</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>334254</v>
+      </c>
+      <c r="D3">
+        <v>92.84999999999999</v>
+      </c>
+      <c r="E3">
+        <v>334254</v>
+      </c>
+      <c r="F3">
+        <v>12.44</v>
+      </c>
+      <c r="G3">
+        <v>8.25</v>
+      </c>
+      <c r="H3">
+        <v>40.42</v>
       </c>
     </row>
   </sheetData>
@@ -526,111 +552,189 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C2">
-        <v>225778</v>
+        <v>948267</v>
       </c>
       <c r="D2">
-        <v>225778</v>
+        <v>263.41</v>
       </c>
       <c r="E2">
-        <v>18.04</v>
+        <v>805386</v>
       </c>
       <c r="F2">
-        <v>6.42</v>
+        <v>27.06</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>9.629999999999999</v>
       </c>
       <c r="H2">
-        <v>62.72</v>
+        <v>40.42</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3">
-        <v>2334175</v>
+        <v>882955</v>
       </c>
       <c r="D3">
-        <v>2319175</v>
+        <v>245.27</v>
       </c>
       <c r="E3">
-        <v>234</v>
+        <v>823957</v>
       </c>
       <c r="F3">
-        <v>141.21</v>
+        <v>65.52</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>43.54</v>
       </c>
       <c r="H3">
-        <v>648.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4">
+        <v>52000</v>
+      </c>
+      <c r="D4">
+        <v>14.44</v>
+      </c>
+      <c r="E4">
+        <v>52000</v>
+      </c>
+      <c r="F4">
+        <v>3.08</v>
+      </c>
+      <c r="G4">
+        <v>2.03</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="C4">
-        <v>156000</v>
-      </c>
-      <c r="D4">
-        <v>156000</v>
-      </c>
-      <c r="E4">
-        <v>9.24</v>
-      </c>
-      <c r="F4">
-        <v>6.09</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>43.33</v>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>40.42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6">
+        <v>193980</v>
+      </c>
+      <c r="D6">
+        <v>53.88</v>
+      </c>
+      <c r="E6">
+        <v>193980</v>
+      </c>
+      <c r="F6">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="G6">
+        <v>6.22</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7">
+        <v>140274</v>
+      </c>
+      <c r="D7">
+        <v>38.97</v>
+      </c>
+      <c r="E7">
+        <v>140274</v>
+      </c>
+      <c r="F7">
+        <v>3.08</v>
+      </c>
+      <c r="G7">
+        <v>2.03</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -640,63 +744,73 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B6">
+        <v>14</v>
+      </c>
+      <c r="C6">
         <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -706,20 +820,35 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="33">
   <si>
     <t>文件名称</t>
   </si>
@@ -49,12 +49,18 @@
     <t>03-03.csv</t>
   </si>
   <si>
+    <t>0304.csv</t>
+  </si>
+  <si>
     <t>02/03/2026</t>
   </si>
   <si>
     <t>03/03/2026</t>
   </si>
   <si>
+    <t>04/03/2026</t>
+  </si>
+  <si>
     <t>日期</t>
   </si>
   <si>
@@ -95,6 +101,9 @@
   </si>
   <si>
     <t>身体乳单瓶</t>
+  </si>
+  <si>
+    <t>身体乳三瓶</t>
   </si>
   <si>
     <t>精华液单瓶</t>
@@ -464,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -498,7 +507,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>1883222</v>
@@ -524,7 +533,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>334254</v>
@@ -542,6 +551,32 @@
         <v>8.25</v>
       </c>
       <c r="H3">
+        <v>40.42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>1967702</v>
+      </c>
+      <c r="D4">
+        <v>546.58</v>
+      </c>
+      <c r="E4">
+        <v>1680968</v>
+      </c>
+      <c r="F4">
+        <v>175</v>
+      </c>
+      <c r="G4">
+        <v>88.41</v>
+      </c>
+      <c r="H4">
         <v>40.42</v>
       </c>
     </row>
@@ -552,41 +587,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2">
         <v>948267</v>
@@ -609,10 +644,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>882955</v>
@@ -635,10 +670,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>52000</v>
@@ -661,10 +696,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -687,10 +722,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>193980</v>
@@ -713,10 +748,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>140274</v>
@@ -734,6 +769,84 @@
         <v>2.03</v>
       </c>
       <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8">
+        <v>903112</v>
+      </c>
+      <c r="D8">
+        <v>250.86</v>
+      </c>
+      <c r="E8">
+        <v>806668</v>
+      </c>
+      <c r="F8">
+        <v>72.16</v>
+      </c>
+      <c r="G8">
+        <v>25.68</v>
+      </c>
+      <c r="H8">
+        <v>40.42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9">
+        <v>908590</v>
+      </c>
+      <c r="D9">
+        <v>252.39</v>
+      </c>
+      <c r="E9">
+        <v>759100</v>
+      </c>
+      <c r="F9">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="G9">
+        <v>56.64</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>156000</v>
+      </c>
+      <c r="D10">
+        <v>43.33</v>
+      </c>
+      <c r="E10">
+        <v>115200</v>
+      </c>
+      <c r="F10">
+        <v>9.24</v>
+      </c>
+      <c r="G10">
+        <v>6.09</v>
+      </c>
+      <c r="H10">
         <v>0</v>
       </c>
     </row>
@@ -744,23 +857,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -768,10 +884,13 @@
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>7</v>
@@ -779,21 +898,27 @@
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -801,16 +926,36 @@
       <c r="C5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
         <v>14</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>2</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -820,26 +965,29 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -848,7 +996,10 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="37">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,22 +43,28 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>03-02.csv</t>
-  </si>
-  <si>
-    <t>03-03.csv</t>
-  </si>
-  <si>
-    <t>0304.csv</t>
-  </si>
-  <si>
-    <t>02/03/2026</t>
-  </si>
-  <si>
-    <t>03/03/2026</t>
-  </si>
-  <si>
-    <t>04/03/2026</t>
+    <t>0308.csv</t>
+  </si>
+  <si>
+    <t>0309.csv</t>
+  </si>
+  <si>
+    <t>0310.csv</t>
+  </si>
+  <si>
+    <t>0311.csv</t>
+  </si>
+  <si>
+    <t>08/03/2026</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>11/03/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -103,13 +109,19 @@
     <t>身体乳单瓶</t>
   </si>
   <si>
-    <t>身体乳三瓶</t>
+    <t>身体乳双瓶</t>
   </si>
   <si>
     <t>精华液单瓶</t>
   </si>
   <si>
     <t>精华液双瓶</t>
+  </si>
+  <si>
+    <t>精华液三瓶</t>
+  </si>
+  <si>
+    <t>精华液&amp;黑鸦片</t>
   </si>
   <si>
     <t>汇总</t>
@@ -473,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -507,25 +519,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>1883222</v>
+        <v>1689775</v>
       </c>
       <c r="D2">
-        <v>523.12</v>
+        <v>469.38</v>
       </c>
       <c r="E2">
-        <v>1681343</v>
+        <v>1562882</v>
       </c>
       <c r="F2">
-        <v>95.66</v>
+        <v>85.61999999999999</v>
       </c>
       <c r="G2">
-        <v>55.2</v>
+        <v>42.96</v>
       </c>
       <c r="H2">
-        <v>40.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,25 +545,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>334254</v>
+        <v>1653304</v>
       </c>
       <c r="D3">
-        <v>92.84999999999999</v>
+        <v>459.25</v>
       </c>
       <c r="E3">
-        <v>334254</v>
+        <v>1404404</v>
       </c>
       <c r="F3">
-        <v>12.44</v>
+        <v>147.04</v>
       </c>
       <c r="G3">
-        <v>8.25</v>
+        <v>72.53</v>
       </c>
       <c r="H3">
-        <v>40.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -559,24 +571,50 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>1967702</v>
+        <v>152533</v>
       </c>
       <c r="D4">
-        <v>546.58</v>
+        <v>42.37</v>
       </c>
       <c r="E4">
-        <v>1680968</v>
+        <v>152533</v>
       </c>
       <c r="F4">
-        <v>175</v>
+        <v>18.72</v>
       </c>
       <c r="G4">
-        <v>88.41</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="H4">
+        <v>28.24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>2679319</v>
+      </c>
+      <c r="D5">
+        <v>744.26</v>
+      </c>
+      <c r="E5">
+        <v>2082469</v>
+      </c>
+      <c r="F5">
+        <v>190.86</v>
+      </c>
+      <c r="G5">
+        <v>107.35</v>
+      </c>
+      <c r="H5">
         <v>40.42</v>
       </c>
     </row>
@@ -587,82 +625,82 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2">
-        <v>948267</v>
+        <v>1241779</v>
       </c>
       <c r="D2">
-        <v>263.41</v>
+        <v>344.94</v>
       </c>
       <c r="E2">
-        <v>805386</v>
+        <v>1184686</v>
       </c>
       <c r="F2">
-        <v>27.06</v>
+        <v>45.09999999999999</v>
       </c>
       <c r="G2">
-        <v>9.629999999999999</v>
+        <v>16.05</v>
       </c>
       <c r="H2">
-        <v>40.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C3">
-        <v>882955</v>
+        <v>395996</v>
       </c>
       <c r="D3">
-        <v>245.27</v>
+        <v>110</v>
       </c>
       <c r="E3">
-        <v>823957</v>
+        <v>336596</v>
       </c>
       <c r="F3">
-        <v>65.52</v>
+        <v>37.44</v>
       </c>
       <c r="G3">
-        <v>43.54</v>
+        <v>24.88</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -670,10 +708,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>52000</v>
@@ -682,7 +720,7 @@
         <v>14.44</v>
       </c>
       <c r="E4">
-        <v>52000</v>
+        <v>41600</v>
       </c>
       <c r="F4">
         <v>3.08</v>
@@ -696,51 +734,51 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>903112</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>250.86</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>813112</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>72.16</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>25.68</v>
       </c>
       <c r="H5">
-        <v>40.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6">
-        <v>193980</v>
+        <v>750192</v>
       </c>
       <c r="D6">
-        <v>53.88</v>
+        <v>208.39</v>
       </c>
       <c r="E6">
-        <v>193980</v>
+        <v>591292</v>
       </c>
       <c r="F6">
-        <v>9.359999999999999</v>
+        <v>74.88</v>
       </c>
       <c r="G6">
-        <v>6.22</v>
+        <v>46.85</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -748,25 +786,25 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>140274</v>
+        <v>152533</v>
       </c>
       <c r="D7">
-        <v>38.97</v>
+        <v>42.37</v>
       </c>
       <c r="E7">
-        <v>140274</v>
+        <v>152533</v>
       </c>
       <c r="F7">
-        <v>3.08</v>
+        <v>18.72</v>
       </c>
       <c r="G7">
-        <v>2.03</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -774,79 +812,105 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8">
-        <v>903112</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>250.86</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>806668</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>72.16</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>25.68</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>40.42</v>
+        <v>28.24</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9">
-        <v>908590</v>
+        <v>1325131</v>
       </c>
       <c r="D9">
-        <v>252.39</v>
+        <v>368.09</v>
       </c>
       <c r="E9">
-        <v>759100</v>
+        <v>964331</v>
       </c>
       <c r="F9">
-        <v>93.59999999999999</v>
+        <v>66.22</v>
       </c>
       <c r="G9">
-        <v>56.64</v>
+        <v>27.5</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>40.42</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10">
-        <v>156000</v>
+        <v>1146188</v>
       </c>
       <c r="D10">
-        <v>43.33</v>
+        <v>318.39</v>
       </c>
       <c r="E10">
-        <v>115200</v>
+        <v>955738</v>
       </c>
       <c r="F10">
-        <v>9.24</v>
+        <v>112.32</v>
       </c>
       <c r="G10">
-        <v>6.09</v>
+        <v>71.72999999999999</v>
       </c>
       <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11">
+        <v>208000</v>
+      </c>
+      <c r="D11">
+        <v>57.78</v>
+      </c>
+      <c r="E11">
+        <v>162400</v>
+      </c>
+      <c r="F11">
+        <v>12.32</v>
+      </c>
+      <c r="G11">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H11">
         <v>0</v>
       </c>
     </row>
@@ -857,85 +921,100 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <v>1</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -943,19 +1022,59 @@
       <c r="D6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -965,32 +1084,29 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -998,8 +1114,19 @@
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="E2">
-        <v>6</v>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,28 +43,16 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>0308.csv</t>
-  </si>
-  <si>
-    <t>0309.csv</t>
-  </si>
-  <si>
-    <t>0310.csv</t>
-  </si>
-  <si>
-    <t>0311.csv</t>
+    <t>越南跨境店-0308.csv</t>
+  </si>
+  <si>
+    <t>越南跨境店-0315.csv</t>
   </si>
   <si>
     <t>08/03/2026</t>
   </si>
   <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>10/03/2026</t>
-  </si>
-  <si>
-    <t>11/03/2026</t>
+    <t>15/03/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -106,10 +94,19 @@
     <t>身体乳300ml单瓶</t>
   </si>
   <si>
+    <t>身体乳300ml双瓶</t>
+  </si>
+  <si>
+    <t>身体乳300ml三瓶</t>
+  </si>
+  <si>
     <t>身体乳单瓶</t>
   </si>
   <si>
     <t>身体乳双瓶</t>
+  </si>
+  <si>
+    <t>身体乳三瓶</t>
   </si>
   <si>
     <t>精华液单瓶</t>
@@ -485,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -519,25 +516,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>1689775</v>
+        <v>9856699</v>
       </c>
       <c r="D2">
-        <v>469.38</v>
+        <v>2737.97</v>
       </c>
       <c r="E2">
-        <v>1562882</v>
+        <v>8874895</v>
       </c>
       <c r="F2">
-        <v>85.61999999999999</v>
+        <v>680.36</v>
       </c>
       <c r="G2">
-        <v>42.96</v>
+        <v>339.9</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>222.31</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -545,77 +542,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>1653304</v>
+        <v>12462631</v>
       </c>
       <c r="D3">
-        <v>459.25</v>
+        <v>3461.84</v>
       </c>
       <c r="E3">
-        <v>1404404</v>
+        <v>10446424</v>
       </c>
       <c r="F3">
-        <v>147.04</v>
+        <v>928.9999999999999</v>
       </c>
       <c r="G3">
-        <v>72.53</v>
+        <v>485.58</v>
       </c>
       <c r="H3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4">
-        <v>152533</v>
-      </c>
-      <c r="D4">
-        <v>42.37</v>
-      </c>
-      <c r="E4">
-        <v>152533</v>
-      </c>
-      <c r="F4">
-        <v>18.72</v>
-      </c>
-      <c r="G4">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="H4">
-        <v>28.24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>2679319</v>
-      </c>
-      <c r="D5">
-        <v>744.26</v>
-      </c>
-      <c r="E5">
-        <v>2082469</v>
-      </c>
-      <c r="F5">
-        <v>190.86</v>
-      </c>
-      <c r="G5">
-        <v>107.35</v>
-      </c>
-      <c r="H5">
-        <v>40.42</v>
+        <v>161.68</v>
       </c>
     </row>
   </sheetData>
@@ -625,82 +570,82 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C2">
-        <v>1241779</v>
+        <v>5102582</v>
       </c>
       <c r="D2">
-        <v>344.94</v>
+        <v>1417.38</v>
       </c>
       <c r="E2">
-        <v>1184686</v>
+        <v>4661064</v>
       </c>
       <c r="F2">
-        <v>45.09999999999999</v>
+        <v>234.52</v>
       </c>
       <c r="G2">
-        <v>16.05</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>222.31</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C3">
-        <v>395996</v>
+        <v>4244517</v>
       </c>
       <c r="D3">
-        <v>110</v>
+        <v>1179.03</v>
       </c>
       <c r="E3">
-        <v>336596</v>
+        <v>3792871</v>
       </c>
       <c r="F3">
-        <v>37.44</v>
+        <v>421.2</v>
       </c>
       <c r="G3">
-        <v>24.88</v>
+        <v>240.2</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -708,25 +653,25 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C4">
-        <v>52000</v>
+        <v>509600</v>
       </c>
       <c r="D4">
-        <v>14.44</v>
+        <v>141.56</v>
       </c>
       <c r="E4">
-        <v>41600</v>
+        <v>420960</v>
       </c>
       <c r="F4">
-        <v>3.08</v>
+        <v>24.64</v>
       </c>
       <c r="G4">
-        <v>2.03</v>
+        <v>16.24</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -734,51 +679,51 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C5">
-        <v>903112</v>
+        <v>6247092</v>
       </c>
       <c r="D5">
-        <v>250.86</v>
+        <v>1735.3</v>
       </c>
       <c r="E5">
-        <v>813112</v>
+        <v>5338085</v>
       </c>
       <c r="F5">
-        <v>72.16</v>
+        <v>345.84</v>
       </c>
       <c r="G5">
-        <v>25.68</v>
+        <v>127.01</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>161.68</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C6">
-        <v>750192</v>
+        <v>5711139</v>
       </c>
       <c r="D6">
-        <v>208.39</v>
+        <v>1586.43</v>
       </c>
       <c r="E6">
-        <v>591292</v>
+        <v>4705439</v>
       </c>
       <c r="F6">
-        <v>74.88</v>
+        <v>561.5999999999999</v>
       </c>
       <c r="G6">
-        <v>46.85</v>
+        <v>344.36</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -786,131 +731,27 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C7">
-        <v>152533</v>
+        <v>504400</v>
       </c>
       <c r="D7">
-        <v>42.37</v>
+        <v>140.11</v>
       </c>
       <c r="E7">
-        <v>152533</v>
+        <v>402900</v>
       </c>
       <c r="F7">
-        <v>18.72</v>
+        <v>21.56</v>
       </c>
       <c r="G7">
-        <v>9.529999999999999</v>
+        <v>14.21</v>
       </c>
       <c r="H7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>28.24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9">
-        <v>1325131</v>
-      </c>
-      <c r="D9">
-        <v>368.09</v>
-      </c>
-      <c r="E9">
-        <v>964331</v>
-      </c>
-      <c r="F9">
-        <v>66.22</v>
-      </c>
-      <c r="G9">
-        <v>27.5</v>
-      </c>
-      <c r="H9">
-        <v>40.42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10">
-        <v>1146188</v>
-      </c>
-      <c r="D10">
-        <v>318.39</v>
-      </c>
-      <c r="E10">
-        <v>955738</v>
-      </c>
-      <c r="F10">
-        <v>112.32</v>
-      </c>
-      <c r="G10">
-        <v>71.72999999999999</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11">
-        <v>208000</v>
-      </c>
-      <c r="D11">
-        <v>57.78</v>
-      </c>
-      <c r="E11">
-        <v>162400</v>
-      </c>
-      <c r="F11">
-        <v>12.32</v>
-      </c>
-      <c r="G11">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="H11">
         <v>0</v>
       </c>
     </row>
@@ -921,63 +762,45 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="C2">
+      <c r="C3">
         <v>0</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>6</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -985,96 +808,93 @@
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5">
+        <v>21</v>
+      </c>
+      <c r="C5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="E4">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8">
+        <v>26</v>
+      </c>
+      <c r="C8">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>8</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9">
-        <v>13</v>
-      </c>
-      <c r="C9">
-        <v>15</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>24</v>
+      <c r="B12">
+        <v>76</v>
+      </c>
+      <c r="C12">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1084,49 +904,35 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,16 +43,16 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>越南跨境店-0308.csv</t>
-  </si>
-  <si>
-    <t>越南跨境店-0315.csv</t>
-  </si>
-  <si>
-    <t>08/03/2026</t>
-  </si>
-  <si>
-    <t>15/03/2026</t>
+    <t>0316.csv</t>
+  </si>
+  <si>
+    <t>0317.csv</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -85,21 +85,9 @@
     <t>身体乳</t>
   </si>
   <si>
-    <t>身体乳300ml</t>
-  </si>
-  <si>
     <t>商品名称</t>
   </si>
   <si>
-    <t>身体乳300ml单瓶</t>
-  </si>
-  <si>
-    <t>身体乳300ml双瓶</t>
-  </si>
-  <si>
-    <t>身体乳300ml三瓶</t>
-  </si>
-  <si>
     <t>身体乳单瓶</t>
   </si>
   <si>
@@ -116,9 +104,6 @@
   </si>
   <si>
     <t>精华液三瓶</t>
-  </si>
-  <si>
-    <t>精华液&amp;黑鸦片</t>
   </si>
   <si>
     <t>汇总</t>
@@ -519,22 +504,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>9856699</v>
+        <v>2162413</v>
       </c>
       <c r="D2">
-        <v>2737.97</v>
+        <v>600.67</v>
       </c>
       <c r="E2">
-        <v>8874895</v>
+        <v>1934814</v>
       </c>
       <c r="F2">
-        <v>680.36</v>
+        <v>129.68</v>
       </c>
       <c r="G2">
-        <v>339.9</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="H2">
-        <v>222.31</v>
+        <v>40.42</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -545,22 +530,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>12462631</v>
+        <v>2160774</v>
       </c>
       <c r="D3">
-        <v>3461.84</v>
+        <v>600.22</v>
       </c>
       <c r="E3">
-        <v>10446424</v>
+        <v>2016174</v>
       </c>
       <c r="F3">
-        <v>928.9999999999999</v>
+        <v>74.19999999999999</v>
       </c>
       <c r="G3">
-        <v>485.58</v>
+        <v>38.18</v>
       </c>
       <c r="H3">
-        <v>161.68</v>
+        <v>40.42</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +555,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -607,22 +592,22 @@
         <v>20</v>
       </c>
       <c r="C2">
-        <v>5102582</v>
+        <v>1196624</v>
       </c>
       <c r="D2">
-        <v>1417.38</v>
+        <v>332.4</v>
       </c>
       <c r="E2">
-        <v>4661064</v>
+        <v>1147624</v>
       </c>
       <c r="F2">
-        <v>234.52</v>
+        <v>36.08</v>
       </c>
       <c r="G2">
-        <v>83.45999999999999</v>
+        <v>12.84</v>
       </c>
       <c r="H2">
-        <v>222.31</v>
+        <v>40.42</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -633,19 +618,19 @@
         <v>21</v>
       </c>
       <c r="C3">
-        <v>4244517</v>
+        <v>965789</v>
       </c>
       <c r="D3">
-        <v>1179.03</v>
+        <v>268.27</v>
       </c>
       <c r="E3">
-        <v>3792871</v>
+        <v>787190</v>
       </c>
       <c r="F3">
-        <v>421.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G3">
-        <v>240.2</v>
+        <v>53.73</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -653,28 +638,28 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4">
-        <v>509600</v>
+        <v>1648180</v>
       </c>
       <c r="D4">
-        <v>141.56</v>
+        <v>457.83</v>
       </c>
       <c r="E4">
-        <v>420960</v>
+        <v>1543180</v>
       </c>
       <c r="F4">
-        <v>24.64</v>
+        <v>18.04</v>
       </c>
       <c r="G4">
-        <v>16.24</v>
+        <v>6.42</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>40.42</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -682,76 +667,24 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5">
-        <v>6247092</v>
+        <v>512594</v>
       </c>
       <c r="D5">
-        <v>1735.3</v>
+        <v>142.39</v>
       </c>
       <c r="E5">
-        <v>5338085</v>
+        <v>472994</v>
       </c>
       <c r="F5">
-        <v>345.84</v>
+        <v>56.16</v>
       </c>
       <c r="G5">
-        <v>127.01</v>
+        <v>31.76</v>
       </c>
       <c r="H5">
-        <v>161.68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6">
-        <v>5711139</v>
-      </c>
-      <c r="D6">
-        <v>1586.43</v>
-      </c>
-      <c r="E6">
-        <v>4705439</v>
-      </c>
-      <c r="F6">
-        <v>561.5999999999999</v>
-      </c>
-      <c r="G6">
-        <v>344.36</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7">
-        <v>504400</v>
-      </c>
-      <c r="D7">
-        <v>140.11</v>
-      </c>
-      <c r="E7">
-        <v>402900</v>
-      </c>
-      <c r="F7">
-        <v>21.56</v>
-      </c>
-      <c r="G7">
-        <v>14.21</v>
-      </c>
-      <c r="H7">
         <v>0</v>
       </c>
     </row>
@@ -762,12 +695,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -778,18 +711,18 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -800,10 +733,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -811,90 +744,46 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C8">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12">
-        <v>76</v>
-      </c>
-      <c r="C12">
-        <v>104</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -909,7 +798,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -918,21 +807,21 @@
         <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,16 +43,22 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>0316.csv</t>
-  </si>
-  <si>
-    <t>0317.csv</t>
-  </si>
-  <si>
-    <t>16/03/2026</t>
-  </si>
-  <si>
-    <t>17/03/2026</t>
+    <t>0329.csv</t>
+  </si>
+  <si>
+    <t>0330.csv</t>
+  </si>
+  <si>
+    <t>0331.csv</t>
+  </si>
+  <si>
+    <t>29/03/2026</t>
+  </si>
+  <si>
+    <t>30/03/2026</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -85,9 +91,18 @@
     <t>身体乳</t>
   </si>
   <si>
+    <t>身体乳300ml</t>
+  </si>
+  <si>
+    <t>防晒霜</t>
+  </si>
+  <si>
     <t>商品名称</t>
   </si>
   <si>
+    <t>身体乳300ml单瓶</t>
+  </si>
+  <si>
     <t>身体乳单瓶</t>
   </si>
   <si>
@@ -95,6 +110,9 @@
   </si>
   <si>
     <t>身体乳三瓶</t>
+  </si>
+  <si>
+    <t>防晒霜单瓶</t>
   </si>
   <si>
     <t>精华液单瓶</t>
@@ -467,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -501,25 +519,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>2162413</v>
+        <v>1006531</v>
       </c>
       <c r="D2">
-        <v>600.67</v>
+        <v>279.59</v>
       </c>
       <c r="E2">
-        <v>1934814</v>
+        <v>892664</v>
       </c>
       <c r="F2">
-        <v>129.68</v>
+        <v>85.28</v>
       </c>
       <c r="G2">
-        <v>66.56999999999999</v>
+        <v>37.04</v>
       </c>
       <c r="H2">
-        <v>40.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -527,24 +545,50 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>2160774</v>
+        <v>1978171</v>
       </c>
       <c r="D3">
-        <v>600.22</v>
+        <v>549.49</v>
       </c>
       <c r="E3">
-        <v>2016174</v>
+        <v>1666612</v>
       </c>
       <c r="F3">
-        <v>74.19999999999999</v>
+        <v>118.99</v>
       </c>
       <c r="G3">
-        <v>38.18</v>
+        <v>57.17999999999999</v>
       </c>
       <c r="H3">
+        <v>20.21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>706175</v>
+      </c>
+      <c r="D4">
+        <v>196.16</v>
+      </c>
+      <c r="E4">
+        <v>641791</v>
+      </c>
+      <c r="F4">
+        <v>46.12</v>
+      </c>
+      <c r="G4">
+        <v>22.17</v>
+      </c>
+      <c r="H4">
         <v>40.42</v>
       </c>
     </row>
@@ -555,82 +599,82 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2">
-        <v>1196624</v>
+        <v>677334</v>
       </c>
       <c r="D2">
-        <v>332.4</v>
+        <v>188.15</v>
       </c>
       <c r="E2">
-        <v>1147624</v>
+        <v>603467</v>
       </c>
       <c r="F2">
-        <v>36.08</v>
+        <v>54.12</v>
       </c>
       <c r="G2">
-        <v>12.84</v>
+        <v>19.26</v>
       </c>
       <c r="H2">
-        <v>40.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3">
-        <v>965789</v>
+        <v>277197</v>
       </c>
       <c r="D3">
-        <v>268.27</v>
+        <v>77</v>
       </c>
       <c r="E3">
-        <v>787190</v>
+        <v>237197</v>
       </c>
       <c r="F3">
-        <v>93.59999999999999</v>
+        <v>28.08</v>
       </c>
       <c r="G3">
-        <v>53.73</v>
+        <v>15.75</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -641,50 +685,154 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C4">
-        <v>1648180</v>
+        <v>52000</v>
       </c>
       <c r="D4">
-        <v>457.83</v>
+        <v>14.44</v>
       </c>
       <c r="E4">
-        <v>1543180</v>
+        <v>52000</v>
       </c>
       <c r="F4">
-        <v>18.04</v>
+        <v>3.08</v>
       </c>
       <c r="G4">
-        <v>6.42</v>
+        <v>2.03</v>
       </c>
       <c r="H4">
-        <v>40.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5">
-        <v>512594</v>
+        <v>1241779</v>
       </c>
       <c r="D5">
-        <v>142.39</v>
+        <v>344.94</v>
       </c>
       <c r="E5">
-        <v>472994</v>
+        <v>1043430</v>
       </c>
       <c r="F5">
-        <v>56.16</v>
+        <v>45.09999999999999</v>
       </c>
       <c r="G5">
-        <v>31.76</v>
+        <v>16.05</v>
       </c>
       <c r="H5">
+        <v>20.21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6">
+        <v>633593</v>
+      </c>
+      <c r="D6">
+        <v>176</v>
+      </c>
+      <c r="E6">
+        <v>520383</v>
+      </c>
+      <c r="F6">
+        <v>65.52</v>
+      </c>
+      <c r="G6">
+        <v>37.98</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7">
+        <v>102799</v>
+      </c>
+      <c r="D7">
+        <v>28.56</v>
+      </c>
+      <c r="E7">
+        <v>102799</v>
+      </c>
+      <c r="F7">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="G7">
+        <v>3.15</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8">
+        <v>428978</v>
+      </c>
+      <c r="D8">
+        <v>119.16</v>
+      </c>
+      <c r="E8">
+        <v>364594</v>
+      </c>
+      <c r="F8">
+        <v>18.04</v>
+      </c>
+      <c r="G8">
+        <v>6.42</v>
+      </c>
+      <c r="H8">
+        <v>40.42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9">
+        <v>277197</v>
+      </c>
+      <c r="D9">
+        <v>77</v>
+      </c>
+      <c r="E9">
+        <v>277197</v>
+      </c>
+      <c r="F9">
+        <v>28.08</v>
+      </c>
+      <c r="G9">
+        <v>15.75</v>
+      </c>
+      <c r="H9">
         <v>0</v>
       </c>
     </row>
@@ -695,95 +843,147 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6">
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
         <v>1</v>
       </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8">
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
         <v>14</v>
       </c>
-      <c r="C8">
-        <v>12</v>
+      <c r="D10">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -798,30 +998,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="39">
   <si>
     <t>文件名称</t>
   </si>
@@ -52,6 +52,9 @@
     <t>0331.csv</t>
   </si>
   <si>
+    <t>0401.csv</t>
+  </si>
+  <si>
     <t>29/03/2026</t>
   </si>
   <si>
@@ -59,6 +62,9 @@
   </si>
   <si>
     <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>01/04/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -485,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -519,7 +525,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>1006531</v>
@@ -545,7 +551,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>1978171</v>
@@ -560,7 +566,7 @@
         <v>118.99</v>
       </c>
       <c r="G3">
-        <v>57.17999999999999</v>
+        <v>57.18</v>
       </c>
       <c r="H3">
         <v>20.21</v>
@@ -571,7 +577,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>706175</v>
@@ -589,6 +595,32 @@
         <v>22.17</v>
       </c>
       <c r="H4">
+        <v>40.42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>3223423</v>
+      </c>
+      <c r="D5">
+        <v>895.4</v>
+      </c>
+      <c r="E5">
+        <v>2855648</v>
+      </c>
+      <c r="F5">
+        <v>135.98</v>
+      </c>
+      <c r="G5">
+        <v>54.16999999999999</v>
+      </c>
+      <c r="H5">
         <v>40.42</v>
       </c>
     </row>
@@ -599,41 +631,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2">
         <v>677334</v>
@@ -656,10 +688,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>277197</v>
@@ -682,10 +714,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>52000</v>
@@ -708,10 +740,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>1241779</v>
@@ -734,10 +766,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>633593</v>
@@ -760,10 +792,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>102799</v>
@@ -786,10 +818,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8">
         <v>428978</v>
@@ -812,10 +844,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9">
         <v>277197</v>
@@ -833,6 +865,58 @@
         <v>15.75</v>
       </c>
       <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>3025425</v>
+      </c>
+      <c r="D10">
+        <v>840.4</v>
+      </c>
+      <c r="E10">
+        <v>2697250</v>
+      </c>
+      <c r="F10">
+        <v>117.26</v>
+      </c>
+      <c r="G10">
+        <v>41.73</v>
+      </c>
+      <c r="H10">
+        <v>40.42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11">
+        <v>197998</v>
+      </c>
+      <c r="D11">
+        <v>55</v>
+      </c>
+      <c r="E11">
+        <v>158398</v>
+      </c>
+      <c r="F11">
+        <v>18.72</v>
+      </c>
+      <c r="G11">
+        <v>12.44</v>
+      </c>
+      <c r="H11">
         <v>0</v>
       </c>
     </row>
@@ -843,26 +927,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -873,10 +960,13 @@
       <c r="D2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -887,10 +977,13 @@
       <c r="D3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -901,10 +994,13 @@
       <c r="D4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -915,10 +1011,13 @@
       <c r="D5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -929,10 +1028,13 @@
       <c r="D6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -943,10 +1045,13 @@
       <c r="D7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -957,10 +1062,13 @@
       <c r="D8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -971,10 +1079,13 @@
       <c r="D9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -984,6 +1095,9 @@
       </c>
       <c r="D10">
         <v>5</v>
+      </c>
+      <c r="E10">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -993,26 +1107,29 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1021,7 +1138,10 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="41">
   <si>
     <t>文件名称</t>
   </si>
@@ -55,6 +55,9 @@
     <t>0401.csv</t>
   </si>
   <si>
+    <t>0402.csv</t>
+  </si>
+  <si>
     <t>29/03/2026</t>
   </si>
   <si>
@@ -65,6 +68,9 @@
   </si>
   <si>
     <t>01/04/2026</t>
+  </si>
+  <si>
+    <t>02/04/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -491,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -525,7 +531,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>1006531</v>
@@ -537,7 +543,7 @@
         <v>892664</v>
       </c>
       <c r="F2">
-        <v>85.28</v>
+        <v>85.27999999999999</v>
       </c>
       <c r="G2">
         <v>37.04</v>
@@ -551,7 +557,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>1978171</v>
@@ -566,7 +572,7 @@
         <v>118.99</v>
       </c>
       <c r="G3">
-        <v>57.18</v>
+        <v>57.17999999999999</v>
       </c>
       <c r="H3">
         <v>20.21</v>
@@ -577,7 +583,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4">
         <v>706175</v>
@@ -603,7 +609,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>3223423</v>
@@ -621,6 +627,32 @@
         <v>54.16999999999999</v>
       </c>
       <c r="H5">
+        <v>40.42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>942283</v>
+      </c>
+      <c r="D6">
+        <v>261.75</v>
+      </c>
+      <c r="E6">
+        <v>779299</v>
+      </c>
+      <c r="F6">
+        <v>68.25999999999999</v>
+      </c>
+      <c r="G6">
+        <v>39.65</v>
+      </c>
+      <c r="H6">
         <v>40.42</v>
       </c>
     </row>
@@ -631,41 +663,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2">
         <v>677334</v>
@@ -688,10 +720,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>277197</v>
@@ -714,10 +746,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>52000</v>
@@ -740,10 +772,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>1241779</v>
@@ -766,10 +798,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>633593</v>
@@ -792,10 +824,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>102799</v>
@@ -818,10 +850,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8">
         <v>428978</v>
@@ -844,10 +876,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9">
         <v>277197</v>
@@ -870,10 +902,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10">
         <v>3025425</v>
@@ -896,10 +928,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11">
         <v>197998</v>
@@ -917,6 +949,84 @@
         <v>12.44</v>
       </c>
       <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12">
+        <v>316089</v>
+      </c>
+      <c r="D12">
+        <v>87.8</v>
+      </c>
+      <c r="E12">
+        <v>291705</v>
+      </c>
+      <c r="F12">
+        <v>9.02</v>
+      </c>
+      <c r="G12">
+        <v>3.21</v>
+      </c>
+      <c r="H12">
+        <v>40.42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13">
+        <v>574194</v>
+      </c>
+      <c r="D13">
+        <v>159.5</v>
+      </c>
+      <c r="E13">
+        <v>435594</v>
+      </c>
+      <c r="F13">
+        <v>56.16</v>
+      </c>
+      <c r="G13">
+        <v>34.41</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14">
+        <v>52000</v>
+      </c>
+      <c r="D14">
+        <v>14.44</v>
+      </c>
+      <c r="E14">
+        <v>52000</v>
+      </c>
+      <c r="F14">
+        <v>3.08</v>
+      </c>
+      <c r="G14">
+        <v>2.03</v>
+      </c>
+      <c r="H14">
         <v>0</v>
       </c>
     </row>
@@ -927,29 +1037,32 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>16</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -963,10 +1076,13 @@
       <c r="E2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -980,10 +1096,13 @@
       <c r="E3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -997,10 +1116,13 @@
       <c r="E4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1014,10 +1136,13 @@
       <c r="E5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1031,10 +1156,13 @@
       <c r="E6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -1048,10 +1176,13 @@
       <c r="E7">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1065,10 +1196,13 @@
       <c r="E8">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1082,10 +1216,13 @@
       <c r="E9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -1098,6 +1235,9 @@
       </c>
       <c r="E10">
         <v>22</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1107,29 +1247,32 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1141,7 +1284,10 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,34 +43,22 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>0329.csv</t>
-  </si>
-  <si>
-    <t>0330.csv</t>
-  </si>
-  <si>
-    <t>0331.csv</t>
-  </si>
-  <si>
-    <t>0401.csv</t>
-  </si>
-  <si>
-    <t>0402.csv</t>
-  </si>
-  <si>
-    <t>29/03/2026</t>
-  </si>
-  <si>
-    <t>30/03/2026</t>
-  </si>
-  <si>
-    <t>31/03/2026</t>
-  </si>
-  <si>
-    <t>01/04/2026</t>
-  </si>
-  <si>
-    <t>02/04/2026</t>
+    <t>0406.csv</t>
+  </si>
+  <si>
+    <t>0407.csv</t>
+  </si>
+  <si>
+    <t>0408.csv</t>
+  </si>
+  <si>
+    <t>06/04/2026</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>08/04/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -97,18 +85,18 @@
     <t>寄样支出</t>
   </si>
   <si>
+    <t>身体乳</t>
+  </si>
+  <si>
     <t>精华液</t>
   </si>
   <si>
-    <t>身体乳</t>
+    <t>防晒霜</t>
   </si>
   <si>
     <t>身体乳300ml</t>
   </si>
   <si>
-    <t>防晒霜</t>
-  </si>
-  <si>
     <t>商品名称</t>
   </si>
   <si>
@@ -121,16 +109,10 @@
     <t>身体乳双瓶</t>
   </si>
   <si>
-    <t>身体乳三瓶</t>
-  </si>
-  <si>
     <t>防晒霜单瓶</t>
   </si>
   <si>
     <t>精华液单瓶</t>
-  </si>
-  <si>
-    <t>精华液双瓶</t>
   </si>
   <si>
     <t>精华液三瓶</t>
@@ -497,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -531,22 +513,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>1006531</v>
+        <v>98999</v>
       </c>
       <c r="D2">
-        <v>279.59</v>
+        <v>27.5</v>
       </c>
       <c r="E2">
-        <v>892664</v>
+        <v>98999</v>
       </c>
       <c r="F2">
-        <v>85.27999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G2">
-        <v>37.04</v>
+        <v>6.22</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -557,25 +539,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>1978171</v>
+        <v>1439436</v>
       </c>
       <c r="D3">
-        <v>549.49</v>
+        <v>399.84</v>
       </c>
       <c r="E3">
-        <v>1666612</v>
+        <v>1090296</v>
       </c>
       <c r="F3">
-        <v>118.99</v>
+        <v>128.35</v>
       </c>
       <c r="G3">
-        <v>57.17999999999999</v>
+        <v>66.05</v>
       </c>
       <c r="H3">
-        <v>20.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -583,77 +565,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4">
-        <v>706175</v>
+        <v>1437934</v>
       </c>
       <c r="D4">
-        <v>196.16</v>
+        <v>399.43</v>
       </c>
       <c r="E4">
-        <v>641791</v>
+        <v>1145234</v>
       </c>
       <c r="F4">
-        <v>46.12</v>
+        <v>93.61999999999999</v>
       </c>
       <c r="G4">
-        <v>22.17</v>
+        <v>37.14</v>
       </c>
       <c r="H4">
-        <v>40.42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5">
-        <v>3223423</v>
-      </c>
-      <c r="D5">
-        <v>895.4</v>
-      </c>
-      <c r="E5">
-        <v>2855648</v>
-      </c>
-      <c r="F5">
-        <v>135.98</v>
-      </c>
-      <c r="G5">
-        <v>54.16999999999999</v>
-      </c>
-      <c r="H5">
-        <v>40.42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>942283</v>
-      </c>
-      <c r="D6">
-        <v>261.75</v>
-      </c>
-      <c r="E6">
-        <v>779299</v>
-      </c>
-      <c r="F6">
-        <v>68.25999999999999</v>
-      </c>
-      <c r="G6">
-        <v>39.65</v>
-      </c>
-      <c r="H6">
-        <v>40.42</v>
+        <v>20.21</v>
       </c>
     </row>
   </sheetData>
@@ -663,56 +593,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C2">
-        <v>677334</v>
+        <v>98999</v>
       </c>
       <c r="D2">
-        <v>188.15</v>
+        <v>27.5</v>
       </c>
       <c r="E2">
-        <v>603467</v>
+        <v>98999</v>
       </c>
       <c r="F2">
-        <v>54.12</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G2">
-        <v>19.26</v>
+        <v>6.22</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -720,25 +650,25 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C3">
-        <v>277197</v>
+        <v>564445</v>
       </c>
       <c r="D3">
-        <v>77</v>
+        <v>156.79</v>
       </c>
       <c r="E3">
-        <v>237197</v>
+        <v>449445</v>
       </c>
       <c r="F3">
-        <v>28.08</v>
+        <v>45.09999999999999</v>
       </c>
       <c r="G3">
-        <v>15.75</v>
+        <v>16.05</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -746,25 +676,25 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C4">
-        <v>52000</v>
+        <v>772192</v>
       </c>
       <c r="D4">
-        <v>14.44</v>
+        <v>214.5</v>
       </c>
       <c r="E4">
-        <v>52000</v>
+        <v>588052</v>
       </c>
       <c r="F4">
-        <v>3.08</v>
+        <v>74.88</v>
       </c>
       <c r="G4">
-        <v>2.03</v>
+        <v>46.85</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -772,77 +702,77 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5">
-        <v>1241779</v>
+        <v>102799</v>
       </c>
       <c r="D5">
-        <v>344.94</v>
+        <v>28.56</v>
       </c>
       <c r="E5">
-        <v>1043430</v>
+        <v>52799</v>
       </c>
       <c r="F5">
-        <v>45.09999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G5">
-        <v>16.05</v>
+        <v>3.15</v>
       </c>
       <c r="H5">
-        <v>20.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>633593</v>
+        <v>1286935</v>
       </c>
       <c r="D6">
-        <v>176</v>
+        <v>357.48</v>
       </c>
       <c r="E6">
-        <v>520383</v>
+        <v>1036935</v>
       </c>
       <c r="F6">
-        <v>65.52</v>
+        <v>81.17999999999999</v>
       </c>
       <c r="G6">
-        <v>37.98</v>
+        <v>28.89</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>20.21</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C7">
-        <v>102799</v>
+        <v>98999</v>
       </c>
       <c r="D7">
-        <v>28.56</v>
+        <v>27.5</v>
       </c>
       <c r="E7">
-        <v>102799</v>
+        <v>69299</v>
       </c>
       <c r="F7">
-        <v>8.369999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G7">
-        <v>3.15</v>
+        <v>6.22</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -850,183 +780,27 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8">
-        <v>428978</v>
+        <v>52000</v>
       </c>
       <c r="D8">
-        <v>119.16</v>
+        <v>14.44</v>
       </c>
       <c r="E8">
-        <v>364594</v>
+        <v>39000</v>
       </c>
       <c r="F8">
-        <v>18.04</v>
+        <v>3.08</v>
       </c>
       <c r="G8">
-        <v>6.42</v>
+        <v>2.03</v>
       </c>
       <c r="H8">
-        <v>40.42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9">
-        <v>277197</v>
-      </c>
-      <c r="D9">
-        <v>77</v>
-      </c>
-      <c r="E9">
-        <v>277197</v>
-      </c>
-      <c r="F9">
-        <v>28.08</v>
-      </c>
-      <c r="G9">
-        <v>15.75</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10">
-        <v>3025425</v>
-      </c>
-      <c r="D10">
-        <v>840.4</v>
-      </c>
-      <c r="E10">
-        <v>2697250</v>
-      </c>
-      <c r="F10">
-        <v>117.26</v>
-      </c>
-      <c r="G10">
-        <v>41.73</v>
-      </c>
-      <c r="H10">
-        <v>40.42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11">
-        <v>197998</v>
-      </c>
-      <c r="D11">
-        <v>55</v>
-      </c>
-      <c r="E11">
-        <v>158398</v>
-      </c>
-      <c r="F11">
-        <v>18.72</v>
-      </c>
-      <c r="G11">
-        <v>12.44</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12">
-        <v>316089</v>
-      </c>
-      <c r="D12">
-        <v>87.8</v>
-      </c>
-      <c r="E12">
-        <v>291705</v>
-      </c>
-      <c r="F12">
-        <v>9.02</v>
-      </c>
-      <c r="G12">
-        <v>3.21</v>
-      </c>
-      <c r="H12">
-        <v>40.42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13">
-        <v>574194</v>
-      </c>
-      <c r="D13">
-        <v>159.5</v>
-      </c>
-      <c r="E13">
-        <v>435594</v>
-      </c>
-      <c r="F13">
-        <v>56.16</v>
-      </c>
-      <c r="G13">
-        <v>34.41</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14">
-        <v>52000</v>
-      </c>
-      <c r="D14">
-        <v>14.44</v>
-      </c>
-      <c r="E14">
-        <v>52000</v>
-      </c>
-      <c r="F14">
-        <v>3.08</v>
-      </c>
-      <c r="G14">
-        <v>2.03</v>
-      </c>
-      <c r="H14">
         <v>0</v>
       </c>
     </row>
@@ -1037,92 +811,68 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <v>1</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
       <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1133,111 +883,47 @@
       <c r="D5">
         <v>0</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
         <v>13</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
       <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>5</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10">
-        <v>9</v>
-      </c>
-      <c r="C10">
-        <v>14</v>
-      </c>
-      <c r="D10">
-        <v>5</v>
-      </c>
-      <c r="E10">
-        <v>22</v>
-      </c>
-      <c r="F10">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1247,47 +933,29 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,22 +43,16 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>0406.csv</t>
-  </si>
-  <si>
-    <t>0407.csv</t>
-  </si>
-  <si>
-    <t>0408.csv</t>
-  </si>
-  <si>
-    <t>06/04/2026</t>
-  </si>
-  <si>
-    <t>07/04/2026</t>
-  </si>
-  <si>
-    <t>08/04/2026</t>
+    <t>0503week.csv</t>
+  </si>
+  <si>
+    <t>0510week.csv</t>
+  </si>
+  <si>
+    <t>03/05/2026</t>
+  </si>
+  <si>
+    <t>10/05/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -85,37 +79,43 @@
     <t>寄样支出</t>
   </si>
   <si>
+    <t>其他</t>
+  </si>
+  <si>
     <t>身体乳</t>
   </si>
   <si>
-    <t>精华液</t>
+    <t>身体乳300ml</t>
   </si>
   <si>
     <t>防晒霜</t>
   </si>
   <si>
-    <t>身体乳300ml</t>
-  </si>
-  <si>
     <t>商品名称</t>
   </si>
   <si>
     <t>身体乳300ml单瓶</t>
   </si>
   <si>
+    <t>身体乳300ml双瓶</t>
+  </si>
+  <si>
     <t>身体乳单瓶</t>
   </si>
   <si>
     <t>身体乳双瓶</t>
   </si>
   <si>
+    <t>身体乳三瓶</t>
+  </si>
+  <si>
     <t>防晒霜单瓶</t>
   </si>
   <si>
-    <t>精华液单瓶</t>
-  </si>
-  <si>
-    <t>精华液三瓶</t>
+    <t>唇部精华单支</t>
+  </si>
+  <si>
+    <t>唇部精华双支</t>
   </si>
   <si>
     <t>汇总</t>
@@ -128,16 +128,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -153,7 +145,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -161,30 +153,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -479,32 +453,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -513,25 +487,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>98999</v>
+        <v>5441633</v>
       </c>
       <c r="D2">
-        <v>27.5</v>
+        <v>1511.56</v>
       </c>
       <c r="E2">
-        <v>98999</v>
+        <v>4209202</v>
       </c>
       <c r="F2">
-        <v>9.359999999999999</v>
+        <v>498.17</v>
       </c>
       <c r="G2">
-        <v>6.22</v>
+        <v>306.5599999999999</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>142.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -539,51 +513,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>1439436</v>
+        <v>2725626</v>
       </c>
       <c r="D3">
-        <v>399.84</v>
+        <v>757.12</v>
       </c>
       <c r="E3">
-        <v>1090296</v>
+        <v>2253849</v>
       </c>
       <c r="F3">
-        <v>128.35</v>
+        <v>275.38</v>
       </c>
       <c r="G3">
-        <v>66.05</v>
+        <v>170.33</v>
       </c>
       <c r="H3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4">
-        <v>1437934</v>
-      </c>
-      <c r="D4">
-        <v>399.43</v>
-      </c>
-      <c r="E4">
-        <v>1145234</v>
-      </c>
-      <c r="F4">
-        <v>93.61999999999999</v>
-      </c>
-      <c r="G4">
-        <v>37.14</v>
-      </c>
-      <c r="H4">
-        <v>20.21</v>
+        <v>60.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -593,82 +541,82 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" t="s">
         <v>19</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2">
-        <v>98999</v>
+        <v>699980</v>
       </c>
       <c r="D2">
-        <v>27.5</v>
+        <v>194.44</v>
       </c>
       <c r="E2">
-        <v>98999</v>
+        <v>624980</v>
       </c>
       <c r="F2">
-        <v>9.359999999999999</v>
+        <v>53.2</v>
       </c>
       <c r="G2">
-        <v>6.22</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>142.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C3">
-        <v>564445</v>
+        <v>4322754</v>
       </c>
       <c r="D3">
-        <v>156.79</v>
+        <v>1200.77</v>
       </c>
       <c r="E3">
-        <v>449445</v>
+        <v>3280568</v>
       </c>
       <c r="F3">
-        <v>45.09999999999999</v>
+        <v>421.2</v>
       </c>
       <c r="G3">
-        <v>16.05</v>
+        <v>268.26</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -676,25 +624,25 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4">
-        <v>772192</v>
+        <v>323600</v>
       </c>
       <c r="D4">
-        <v>214.5</v>
+        <v>89.89</v>
       </c>
       <c r="E4">
-        <v>588052</v>
+        <v>223355</v>
       </c>
       <c r="F4">
-        <v>74.88</v>
+        <v>15.4</v>
       </c>
       <c r="G4">
-        <v>46.85</v>
+        <v>10.15</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -702,19 +650,19 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5">
-        <v>102799</v>
+        <v>95299</v>
       </c>
       <c r="D5">
-        <v>28.56</v>
+        <v>26.47</v>
       </c>
       <c r="E5">
-        <v>52799</v>
+        <v>80299</v>
       </c>
       <c r="F5">
         <v>8.369999999999999</v>
@@ -728,51 +676,51 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C6">
-        <v>1286935</v>
+        <v>362750</v>
       </c>
       <c r="D6">
-        <v>357.48</v>
+        <v>100.76</v>
       </c>
       <c r="E6">
-        <v>1036935</v>
+        <v>348750</v>
       </c>
       <c r="F6">
-        <v>81.17999999999999</v>
+        <v>33.25</v>
       </c>
       <c r="G6">
-        <v>28.89</v>
+        <v>17.5</v>
       </c>
       <c r="H6">
-        <v>20.21</v>
+        <v>60.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7">
-        <v>98999</v>
+        <v>1993077</v>
       </c>
       <c r="D7">
-        <v>27.5</v>
+        <v>553.63</v>
       </c>
       <c r="E7">
-        <v>69299</v>
+        <v>1596025</v>
       </c>
       <c r="F7">
-        <v>9.359999999999999</v>
+        <v>215.28</v>
       </c>
       <c r="G7">
-        <v>6.22</v>
+        <v>137.5</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -780,27 +728,53 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C8">
-        <v>52000</v>
+        <v>267000</v>
       </c>
       <c r="D8">
-        <v>14.44</v>
+        <v>74.17</v>
       </c>
       <c r="E8">
-        <v>39000</v>
+        <v>220275</v>
       </c>
       <c r="F8">
-        <v>3.08</v>
+        <v>18.48</v>
       </c>
       <c r="G8">
-        <v>2.03</v>
+        <v>12.18</v>
       </c>
       <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9">
+        <v>102799</v>
+      </c>
+      <c r="D9">
+        <v>28.56</v>
+      </c>
+      <c r="E9">
+        <v>88799</v>
+      </c>
+      <c r="F9">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="G9">
+        <v>3.15</v>
+      </c>
+      <c r="H9">
         <v>0</v>
       </c>
     </row>
@@ -811,119 +785,117 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>6</v>
-      </c>
-      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4">
+        <v>37</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7">
         <v>1</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>31</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
         <v>5</v>
       </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>32</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>33</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>13</v>
-      </c>
-      <c r="D8">
-        <v>12</v>
+      <c r="B10">
+        <v>54</v>
+      </c>
+      <c r="C10">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -933,29 +905,35 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>31</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_VN_cross_border.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView windowWidth="28800" windowHeight="10800"/>
   </bookViews>
   <sheets>
     <sheet name="Weekly Summary" sheetId="1" r:id="rId1"/>
@@ -12,12 +12,25 @@
     <sheet name="Quantity Pivot" sheetId="3" r:id="rId3"/>
     <sheet name="Sample Statistics" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="46">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,16 +56,28 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>0503week.csv</t>
-  </si>
-  <si>
-    <t>0510week.csv</t>
-  </si>
-  <si>
-    <t>03/05/2026</t>
-  </si>
-  <si>
-    <t>10/05/2026</t>
+    <t>越南跨境店-2月份.csv</t>
+  </si>
+  <si>
+    <t>28/02/2026</t>
+  </si>
+  <si>
+    <t>越南跨境店-3月份.csv</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>越南跨境店-4月份.csv</t>
+  </si>
+  <si>
+    <t>30/04/2026</t>
+  </si>
+  <si>
+    <t>越南跨境店-5月份.csv</t>
+  </si>
+  <si>
+    <t>31/05/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -79,18 +104,21 @@
     <t>寄样支出</t>
   </si>
   <si>
+    <t>精华液</t>
+  </si>
+  <si>
+    <t>身体乳</t>
+  </si>
+  <si>
+    <t>身体乳300ml</t>
+  </si>
+  <si>
+    <t>防晒霜</t>
+  </si>
+  <si>
     <t>其他</t>
   </si>
   <si>
-    <t>身体乳</t>
-  </si>
-  <si>
-    <t>身体乳300ml</t>
-  </si>
-  <si>
-    <t>防晒霜</t>
-  </si>
-  <si>
     <t>商品名称</t>
   </si>
   <si>
@@ -100,6 +128,9 @@
     <t>身体乳300ml双瓶</t>
   </si>
   <si>
+    <t>身体乳300ml三瓶</t>
+  </si>
+  <si>
     <t>身体乳单瓶</t>
   </si>
   <si>
@@ -112,10 +143,25 @@
     <t>防晒霜单瓶</t>
   </si>
   <si>
+    <t>防晒霜双瓶</t>
+  </si>
+  <si>
+    <t>精华液单瓶</t>
+  </si>
+  <si>
+    <t>精华液双瓶</t>
+  </si>
+  <si>
+    <t>精华液三瓶</t>
+  </si>
+  <si>
     <t>唇部精华单支</t>
   </si>
   <si>
     <t>唇部精华双支</t>
+  </si>
+  <si>
+    <t>精华液&amp;黑鸦片</t>
   </si>
   <si>
     <t>汇总</t>
@@ -127,25 +173,368 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -153,18 +542,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -447,16 +1131,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="3" max="3" width="14.0769230769231"/>
+    <col min="6" max="6" width="14.0769230769231"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -482,141 +1170,259 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>27182545</v>
+      </c>
+      <c r="D2">
+        <v>7000.4</v>
+      </c>
+      <c r="E2">
+        <v>24022415</v>
+      </c>
+      <c r="F2">
+        <v>2009.22</v>
+      </c>
+      <c r="G2">
+        <v>1148.09</v>
+      </c>
+      <c r="H2">
+        <v>626.51</v>
+      </c>
+      <c r="J2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
         <v>10</v>
-      </c>
-      <c r="C2">
-        <v>5441633</v>
-      </c>
-      <c r="D2">
-        <v>1511.56</v>
-      </c>
-      <c r="E2">
-        <v>4209202</v>
-      </c>
-      <c r="F2">
-        <v>498.17</v>
-      </c>
-      <c r="G2">
-        <v>306.5599999999999</v>
-      </c>
-      <c r="H2">
-        <v>142.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
       </c>
       <c r="C3">
-        <v>2725626</v>
+        <v>45388603</v>
       </c>
       <c r="D3">
-        <v>757.12</v>
+        <v>11689.06</v>
       </c>
       <c r="E3">
-        <v>2253849</v>
+        <v>39534105</v>
       </c>
       <c r="F3">
-        <v>275.38</v>
+        <v>3053.19</v>
       </c>
       <c r="G3">
-        <v>170.33</v>
+        <v>1506.09</v>
       </c>
       <c r="H3">
-        <v>60.90000000000001</v>
+        <v>848.82</v>
+      </c>
+      <c r="J3">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>27415304</v>
+      </c>
+      <c r="D4">
+        <v>7060.34</v>
+      </c>
+      <c r="E4">
+        <v>21991048</v>
+      </c>
+      <c r="F4">
+        <v>2129.5</v>
+      </c>
+      <c r="G4">
+        <v>1169.09</v>
+      </c>
+      <c r="H4">
+        <v>677.83</v>
+      </c>
+      <c r="J4">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>20885615</v>
+      </c>
+      <c r="D5">
+        <v>5378.73</v>
+      </c>
+      <c r="E5">
+        <v>18888924</v>
+      </c>
+      <c r="F5">
+        <v>2643.58</v>
+      </c>
+      <c r="G5">
+        <v>1460.5</v>
+      </c>
+      <c r="H5">
+        <v>429.48</v>
+      </c>
+      <c r="J5">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="C6">
+        <f>C2/J2</f>
+        <v>120276.747787611</v>
+      </c>
+      <c r="E6">
+        <v>-1996.66</v>
+      </c>
+      <c r="F6">
+        <f>E6/J2</f>
+        <v>-8.83477876106195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="C7">
+        <f>C3/J3</f>
+        <v>128216.392655367</v>
+      </c>
+      <c r="E7">
+        <v>-2641.42</v>
+      </c>
+      <c r="F7">
+        <f>E7/J3</f>
+        <v>-7.4616384180791</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="C8">
+        <f>C4/J4</f>
+        <v>117159.418803419</v>
+      </c>
+      <c r="E8">
+        <v>-2264</v>
+      </c>
+      <c r="F8">
+        <f>E8/J4</f>
+        <v>-9.67521367521367</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="C9">
+        <f>C5/J5</f>
+        <v>62531.7814371257</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-3141.18</v>
+      </c>
+      <c r="F9">
+        <f>E9/J5</f>
+        <v>-9.40473053892216</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C2">
-        <v>699980</v>
+        <v>9117433</v>
       </c>
       <c r="D2">
-        <v>194.44</v>
+        <v>2348.04</v>
       </c>
       <c r="E2">
-        <v>624980</v>
+        <v>7987765</v>
       </c>
       <c r="F2">
-        <v>53.2</v>
+        <v>424.16</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>162.75</v>
       </c>
       <c r="H2">
-        <v>142.1</v>
+        <v>626.51</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C3">
-        <v>4322754</v>
+        <v>15289838</v>
       </c>
       <c r="D3">
-        <v>1200.77</v>
+        <v>3937.64</v>
       </c>
       <c r="E3">
-        <v>3280568</v>
+        <v>13816758</v>
       </c>
       <c r="F3">
-        <v>421.2</v>
+        <v>1488.24</v>
       </c>
       <c r="G3">
-        <v>268.26</v>
+        <v>926.26</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -624,25 +1430,25 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C4">
-        <v>323600</v>
+        <v>2199600</v>
       </c>
       <c r="D4">
-        <v>89.89</v>
+        <v>566.47</v>
       </c>
       <c r="E4">
-        <v>223355</v>
+        <v>1684974</v>
       </c>
       <c r="F4">
-        <v>15.4</v>
+        <v>80.08</v>
       </c>
       <c r="G4">
-        <v>10.15</v>
+        <v>52.78</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -650,25 +1456,25 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C5">
-        <v>95299</v>
+        <v>575674</v>
       </c>
       <c r="D5">
-        <v>26.47</v>
+        <v>148.25</v>
       </c>
       <c r="E5">
-        <v>80299</v>
+        <v>532918</v>
       </c>
       <c r="F5">
-        <v>8.369999999999999</v>
+        <v>16.74</v>
       </c>
       <c r="G5">
-        <v>3.15</v>
+        <v>6.3</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -679,25 +1485,25 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>362750</v>
+        <v>27063823</v>
       </c>
       <c r="D6">
-        <v>100.76</v>
+        <v>6969.82</v>
       </c>
       <c r="E6">
-        <v>348750</v>
+        <v>23990732</v>
       </c>
       <c r="F6">
-        <v>33.25</v>
+        <v>1310.98</v>
       </c>
       <c r="G6">
-        <v>17.5</v>
+        <v>470.48</v>
       </c>
       <c r="H6">
-        <v>60.90000000000001</v>
+        <v>848.82</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -705,22 +1511,22 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>1993077</v>
+        <v>16663381</v>
       </c>
       <c r="D7">
-        <v>553.63</v>
+        <v>4291.37</v>
       </c>
       <c r="E7">
-        <v>1596025</v>
+        <v>14214811</v>
       </c>
       <c r="F7">
-        <v>215.28</v>
+        <v>1666.08</v>
       </c>
       <c r="G7">
-        <v>137.5</v>
+        <v>987.8</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -731,22 +1537,22 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8">
-        <v>267000</v>
+        <v>1558600</v>
       </c>
       <c r="D8">
-        <v>74.17</v>
+        <v>401.39</v>
       </c>
       <c r="E8">
-        <v>220275</v>
+        <v>1225763</v>
       </c>
       <c r="F8">
-        <v>18.48</v>
+        <v>67.76</v>
       </c>
       <c r="G8">
-        <v>12.18</v>
+        <v>44.66</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -757,19 +1563,19 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C9">
         <v>102799</v>
       </c>
       <c r="D9">
-        <v>28.56</v>
+        <v>26.47</v>
       </c>
       <c r="E9">
-        <v>88799</v>
+        <v>102799</v>
       </c>
       <c r="F9">
-        <v>8.369999999999999</v>
+        <v>8.37</v>
       </c>
       <c r="G9">
         <v>3.15</v>
@@ -778,107 +1584,391 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10">
+        <v>376700</v>
+      </c>
+      <c r="D10">
+        <v>97.01</v>
+      </c>
+      <c r="E10">
+        <v>316700</v>
+      </c>
+      <c r="F10">
+        <v>26.6</v>
+      </c>
+      <c r="G10">
+        <v>14</v>
+      </c>
+      <c r="H10">
+        <v>516.15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
+        <v>9889076</v>
+      </c>
+      <c r="D11">
+        <v>2546.76</v>
+      </c>
+      <c r="E11">
+        <v>8280051</v>
+      </c>
+      <c r="F11">
+        <v>487.08</v>
+      </c>
+      <c r="G11">
+        <v>173.34</v>
+      </c>
+      <c r="H11">
+        <v>161.68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12">
+        <v>15528534</v>
+      </c>
+      <c r="D12">
+        <v>3999.11</v>
+      </c>
+      <c r="E12">
+        <v>12116515</v>
+      </c>
+      <c r="F12">
+        <v>1516.32</v>
+      </c>
+      <c r="G12">
+        <v>930.37</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13">
+        <v>1004200</v>
+      </c>
+      <c r="D13">
+        <v>258.61</v>
+      </c>
+      <c r="E13">
+        <v>737156</v>
+      </c>
+      <c r="F13">
+        <v>49.28</v>
+      </c>
+      <c r="G13">
+        <v>32.48</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14">
+        <v>616794</v>
+      </c>
+      <c r="D14">
+        <v>158.84</v>
+      </c>
+      <c r="E14">
+        <v>540626</v>
+      </c>
+      <c r="F14">
+        <v>50.22</v>
+      </c>
+      <c r="G14">
+        <v>18.9</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15">
+        <v>10006830</v>
+      </c>
+      <c r="D15">
+        <v>2577.09</v>
+      </c>
+      <c r="E15">
+        <v>9696669</v>
+      </c>
+      <c r="F15">
+        <v>1556.1</v>
+      </c>
+      <c r="G15">
+        <v>816</v>
+      </c>
+      <c r="H15">
+        <v>345.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16">
+        <v>9847172</v>
+      </c>
+      <c r="D16">
+        <v>2535.97</v>
+      </c>
+      <c r="E16">
+        <v>8327063</v>
+      </c>
+      <c r="F16">
+        <v>1010.88</v>
+      </c>
+      <c r="G16">
+        <v>603.48</v>
+      </c>
+      <c r="H16">
+        <v>70.26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17">
+        <v>635417</v>
+      </c>
+      <c r="D17">
+        <v>163.64</v>
+      </c>
+      <c r="E17">
+        <v>525996</v>
+      </c>
+      <c r="F17">
+        <v>43.12</v>
+      </c>
+      <c r="G17">
+        <v>28.42</v>
+      </c>
+      <c r="H17">
+        <v>14.12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18">
+        <v>396196</v>
+      </c>
+      <c r="D18">
+        <v>102.03</v>
+      </c>
+      <c r="E18">
+        <v>339196</v>
+      </c>
+      <c r="F18">
+        <v>33.48</v>
+      </c>
+      <c r="G18">
+        <v>12.6</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B2">
+        <v>26</v>
+      </c>
+      <c r="C2">
+        <v>22</v>
+      </c>
+      <c r="D2">
+        <v>16</v>
+      </c>
+      <c r="E2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5">
+        <v>120</v>
+      </c>
+      <c r="C5">
+        <v>105</v>
+      </c>
+      <c r="D5">
+        <v>113</v>
+      </c>
+      <c r="E5">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7">
         <v>5</v>
       </c>
-      <c r="C2">
+      <c r="C7">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3">
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4">
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
         <v>37</v>
-      </c>
-      <c r="C4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>32</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -886,57 +1976,266 @@
       <c r="C9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B10">
+        <v>43</v>
+      </c>
+      <c r="C10">
+        <v>144</v>
+      </c>
+      <c r="D10">
         <v>54</v>
       </c>
-      <c r="C10">
-        <v>33</v>
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>31</v>
+      </c>
+      <c r="D11">
+        <v>12</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16">
+        <v>226</v>
+      </c>
+      <c r="C16">
+        <v>354</v>
+      </c>
+      <c r="D16">
+        <v>234</v>
+      </c>
+      <c r="E16">
+        <v>334</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>11</v>
       </c>
       <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>49</v>
+      </c>
+      <c r="E2">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="F2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3">
         <v>31</v>
       </c>
-      <c r="B2">
-        <v>14</v>
-      </c>
-      <c r="C2">
-        <v>6</v>
-      </c>
-      <c r="D2">
-        <v>20</v>
+      <c r="C3">
+        <v>42</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>